--- a/base_de_dados.xlsx
+++ b/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B435F1-396C-4B60-99F8-905263A75F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A794BF20-56A5-4AC7-A7BB-E9A1AF748327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3954" uniqueCount="1483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="1493">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4489,6 +4489,36 @@
   </si>
   <si>
     <t>UNIÃO, PVC, SOLDÁVEL, DN 40MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC soldável azul c/ bucha latão - Tê red.90 sold c/ bucha latão B central - 25 mm -1/2"</t>
+  </si>
+  <si>
+    <t>TÊ COM BUCHA DE LATÃO NA BOLSA CENTRAL, PVC, SOLDÁVEL, DN 25MM X 1/2, INSTALADO EM RAMAL OU SUB-RAMAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Curva 90 soldável - 50 mm</t>
+  </si>
+  <si>
+    <t>CURVA 90 GRAUS, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê 90 soldável - 50 mm</t>
+  </si>
+  <si>
+    <t>TE, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Bucha de redução sold. longa - 50 mm - 25 mm</t>
+  </si>
+  <si>
+    <t>BUCHA DE REDUÇÃO PVC, SOLDÁVEL, LONGA, DN 50 X 25 MM, INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Luva soldável - 50 mm</t>
+  </si>
+  <si>
+    <t>LUVA, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
   </si>
 </sst>
 </file>
@@ -4878,7 +4908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B730"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10725,6 +10755,54 @@
         <v>7</v>
       </c>
     </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A731" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A732" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A733" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A734" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A735" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A736" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10732,7 +10810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D730"/>
+  <dimension ref="A1:D736"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -20961,6 +21039,90 @@
         <v>7</v>
       </c>
     </row>
+    <row r="731" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A731" s="2">
+        <v>89396</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D731" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A732" s="2">
+        <v>103986</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D732" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A733" s="2">
+        <v>104004</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C733" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D733" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A734" s="2">
+        <v>105234</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C734" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D734" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A735" s="2">
+        <v>103995</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C735" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A736" s="2">
+        <v>103982</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C736" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D736" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/base_de_dados.xlsx
+++ b/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A794BF20-56A5-4AC7-A7BB-E9A1AF748327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C7BF4A-821B-48A3-B437-BA9B271A8A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-14505" yWindow="930" windowWidth="14610" windowHeight="15585" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="1493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4052" uniqueCount="1519">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4519,6 +4519,84 @@
   </si>
   <si>
     <t>LUVA, PVC, SOLDÁVEL, DN 50MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Tê de redução 90 soldável - 50 mm - 25 mm</t>
+  </si>
+  <si>
+    <t>TÊ DE REDUÇÃO, PVC, SOLDÁVEL, DN 50MM X 25MM, INSTALADO EM RAMAL DE DISTRIBUIÇÃO DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>PVC rígido soldável - Bucha de redução sold. longa - 50 mm - 32 mm</t>
+  </si>
+  <si>
+    <t>BUCHA DE REDUÇÃO PVC, SOLDÁVEL, LONGA, DN 50 X 32 MM, INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>PVC soldável azul c/ bucha latão - Joelho 90º soldável com bucha de latão - 25 mm - 3/4"</t>
+  </si>
+  <si>
+    <t>JOELHO 90 GRAUS COM BUCHA DE LATÃO, PVC, SOLDÁVEL, DN 25 MM X 3/4", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
+  </si>
+  <si>
+    <t>Bomba Hidráulica - Incêndio - WDM Pumps Brasil - QE 3 I - 10 CV - R191</t>
+  </si>
+  <si>
+    <t>BOMBA CENTRÍFUGA, TRIFÁSICA, 10 CV OU 9,86 HP, HM 85 A 140 M, Q 4,2 A 14,9 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_11/2025_PS</t>
+  </si>
+  <si>
+    <t>Bomba Jockey - Bomba schneider - BC-92 S/T AV 150mm - 1.5CV</t>
+  </si>
+  <si>
+    <t>BOMBA CENTRÍFUGA, TRIFÁSICA, 1,5 CV OU 1,48 HP, HM 10 A 70 M, Q 1,8 A 5,3 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_11/2025_PS</t>
+  </si>
+  <si>
+    <t>Metais - Registro de gaveta bruto ABNT - 1"</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Bucha de redução - 1.1/4" x 1"</t>
+  </si>
+  <si>
+    <t>LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 1 1/4" X 1", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Bucha de redução - 1" x 1/2"</t>
+  </si>
+  <si>
+    <t>LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 1" X 1/2", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_01/2026</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Bucha de redução - 2.1/2" x 1.1/4"</t>
+  </si>
+  <si>
+    <t>Comp 878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA DE REDUÇÃO, EM FERRO GALVANIZADO, 2 1/2" X 1 1/4", CONEXÃO ROSQUEADA, INSTALADO EM REDE DE ALIMENTAÇÃO PARA HIDRANTE - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - ( COMPOSIÇÃO REFERÊNCIA SINAPI 92934) </t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Luva de redução - 1" x 1/2"</t>
+  </si>
+  <si>
+    <t>Metais - Pressostato - 1"</t>
+  </si>
+  <si>
+    <t>Metais - Manômetro - 1"</t>
+  </si>
+  <si>
+    <t>Comp 908</t>
+  </si>
+  <si>
+    <t>Tanque de pressão capacidade 25 lt (p/incendio) (COMPOSIÇÃO REFERÊNCIA:  ORSE 13313)</t>
+  </si>
+  <si>
+    <t>Metais - Tanque de Pressão - Tanque de Pressão 25L</t>
+  </si>
+  <si>
+    <t>Ferro maleável classe 10 - Adapt. p/ cx. d´agua de concreto 150 mm - 2.1/2"</t>
+  </si>
+  <si>
+    <t>ADAPTADOR COM FLANGES LIVRES, PVC, SOLDÁVEL, DN 75 MM X 2 1/2", INSTALADO EM RESERVAÇÃO PREDIAL DE ÁGUA - FORNECIMENTO E INSTALAÇÃO. AF_04/2024</t>
   </si>
 </sst>
 </file>
@@ -4908,7 +4986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B736"/>
+  <dimension ref="A1:B749"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -10797,9 +10875,113 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736" s="3" t="s">
-        <v>1461</v>
+        <v>1493</v>
       </c>
       <c r="B736" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A737" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A738" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A739" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A740" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A741" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A742" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A743" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A744" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A745" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A746" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A747" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A748" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A749" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B749" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10810,7 +10992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D736"/>
+  <dimension ref="A1:D749"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="2" bestFit="1" customWidth="1"/>
@@ -21109,17 +21291,199 @@
         <v>7</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A736" s="2">
-        <v>103982</v>
+        <v>104006</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C736" s="3" t="s">
-        <v>1462</v>
+        <v>1494</v>
       </c>
       <c r="D736" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A737" s="2">
+        <v>105228</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C737" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A738" s="2">
+        <v>94672</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D738" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A739" s="2">
+        <v>102122</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C739" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D739" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A740" s="2">
+        <v>102115</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D740" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A741" s="2">
+        <v>94495</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D741" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A742" s="2">
+        <v>92925</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D742" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A743" s="2">
+        <v>92918</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D743" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A744" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D744" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A745" s="2">
+        <v>92918</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C745" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D745" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A746" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D746" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A747" s="2">
+        <v>101917</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C747" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D747" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A748" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D748" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A749" s="2">
+        <v>94713</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C749" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D749" s="2" t="s">
         <v>7</v>
       </c>
     </row>
